--- a/Hoadon/HDVao/12/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/12/HDDienTuMayTinhTien.xlsx
@@ -302,6 +302,79 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K7" s="6"/>
+      <c r="L7" s="13" t="n">
+        <v>1.5462963E7</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>1237037.0</v>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O7" s="13" t="n">
+        <v>1.67E7</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>

--- a/Hoadon/HDVao/12/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/12/HDDienTuMayTinhTien.xlsx
@@ -313,32 +313,32 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MHN</t>
+          <t>C25MCH</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>14303</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>0313005616</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY CỔ PHẦN SWAT CLEAN HOME</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Lầu 6, Số 16 Đường Đào Duy Anh, Phường Đức Nhuận, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -353,23 +353,240 @@
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="13" t="n">
-        <v>1.5462963E7</v>
+        <v>5140998.0</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>1237037.0</v>
+        <v>411280.0</v>
       </c>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
+        <v>5552278.0</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>C25MTK</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>3502242819</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THOẠI KHANG</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K8" s="6"/>
+      <c r="L8" s="13" t="n">
+        <v>2.1451185E7</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>1716095.0</v>
+      </c>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="n">
+        <v>2.316728E7</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K9" s="6"/>
+      <c r="L9" s="13" t="n">
+        <v>1.5462963E7</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>1237037.0</v>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O9" s="13" t="n">
         <v>1.67E7</v>
       </c>
-      <c r="P7" s="6" t="inlineStr">
+      <c r="P9" s="6" t="inlineStr">
         <is>
           <t>Hóa đơn mới</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>C25MHN</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K10" s="6"/>
+      <c r="L10" s="13" t="n">
+        <v>2962963.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>237037.0</v>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="13" t="n">
+        <v>3200000.0</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HDVao/12/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/12/HDDienTuMayTinhTien.xlsx
@@ -308,37 +308,37 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MCM</t>
+          <t>C25MVN</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>866729</t>
+          <t>211</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>03/12/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>3500817878</t>
+          <t>036084000738</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ SÀI GÒN - VŨNG TÀU</t>
+          <t>HỘ KINH DOANH VŨ VĂN NINH</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Số 36 Nguyễn Thái Học, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>166 Phạm Hồng Thái, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -352,15 +352,13 @@
         </is>
       </c>
       <c r="K7" s="6"/>
-      <c r="L7" s="13" t="n">
-        <v>187549.53</v>
-      </c>
-      <c r="M7" s="13" t="n">
-        <v>9377.47</v>
-      </c>
-      <c r="N7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O7" s="13" t="n">
-        <v>196927.0</v>
+        <v>1.395E7</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -389,7 +387,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>866730</t>
+          <t>866729</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -424,14 +422,14 @@
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="13" t="n">
-        <v>93808.58</v>
+        <v>187549.53</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>4690.42</v>
+        <v>9377.47</v>
       </c>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>98499.0</v>
+        <v>196927.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -460,7 +458,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>867276</t>
+          <t>866730</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -495,14 +493,14 @@
       </c>
       <c r="K9" s="6"/>
       <c r="L9" s="13" t="n">
-        <v>66190.48</v>
+        <v>93808.58</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>3309.52</v>
+        <v>4690.42</v>
       </c>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>69500.0</v>
+        <v>98499.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -526,32 +524,32 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25MDO</t>
+          <t>C25MCM</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>290887</t>
+          <t>867276</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>03/12/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3502397072</t>
+          <t>3500817878</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ SÀI GÒN - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Số 510 Cách mạng tháng tám, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 36 Nguyễn Thái Học, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -566,16 +564,14 @@
       </c>
       <c r="K10" s="6"/>
       <c r="L10" s="13" t="n">
-        <v>740741.0</v>
+        <v>66190.48</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>59259.0</v>
-      </c>
-      <c r="N10" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>3309.52</v>
+      </c>
+      <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>800000.0</v>
+        <v>69500.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -604,12 +600,12 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>293570</t>
+          <t>290887</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -656,6 +652,79 @@
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>C25MDO</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>293570</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3502397072</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XĂNG DẦU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Số 510 Cách mạng tháng tám, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K12" s="6"/>
+      <c r="L12" s="13" t="n">
+        <v>740741.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>59259.0</v>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>
